--- a/backtest_runs/20260410_193731/by_symbol/OLPM/OLPM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/OLPM/OLPM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-136.349999999989</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>101181.7</v>
@@ -679,7 +679,7 @@
         <v>-3454.200000000007</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>97727.5</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>97727.5</v>
@@ -1001,7 +1001,7 @@
         <v>-5181.300000000003</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>103499.65</v>
@@ -1093,7 +1093,7 @@
         <v>-1136.25</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>102363.4</v>
@@ -1231,7 +1231,7 @@
         <v>-45.45000000000711</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>103454.2</v>
@@ -1277,7 +1277,7 @@
         <v>-4499.549999999993</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>98954.64999999999</v>
@@ -1369,7 +1369,7 @@
         <v>-681.7500000000097</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>102636.1</v>
@@ -1461,7 +1461,7 @@
         <v>-181.7999999999961</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>102454.3</v>
@@ -1645,7 +1645,7 @@
         <v>-5453.999999999996</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>103545.1</v>
